--- a/docs/02_基本設計/03_データ設計/KF-BD-003_テーブル定義書.xlsx
+++ b/docs/02_基本設計/03_データ設計/KF-BD-003_テーブル定義書.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D10" s="10" t="n"/>
@@ -685,7 +685,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
@@ -984,7 +983,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
@@ -1179,7 +1177,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
@@ -1436,7 +1433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1518,6 +1515,29 @@
         </is>
       </c>
       <c r="E3" s="8" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>2026/10/04</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>users にログイン失敗回数・ロック解除日時・初期パスワード変更要否・パスワード変更日時の 4 列を追加（Flyway V1__init_schema.sql に反映済み）。テーブル一覧の注記を Flyway 前提に更新</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1543,11 +1563,10 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>※データ型はH2/PostgreSQLで共通利用できるものを想定。詳細設計で確定する。物理削除は行わず、状態・有効フラグで管理する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+          <t>※データ型は PostgreSQL（Flyway マイグレーション V1__init_schema.sql）に合わせる。物理削除は行わず、状態・有効フラグで管理する。</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
@@ -1726,7 +1745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1829,7 +1848,7 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>一意</t>
+          <t>一意。保存・検索とも前後の空白を除いた小文字で扱う（ログインで正規化。ONL-001）</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1874,11 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>BCrypt ハッシュ。平文は保存しない</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -2020,50 +2043,154 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>ログイン失敗回数</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>failed_login_count</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr"/>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n"/>
       <c r="E13" s="8" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr"/>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>既定 0。パスワード不一致のたびに +1。5 回でロックし 0 に戻す。ログイン成功でも 0 に戻す</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
+          <t>ロック解除日時</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>locked_until</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>JST。NULL＝ロックなし。現在時刻がこの日時より前ならロック中（E-017）。ロック開始から 30 分後を設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>初期パスワード変更要否</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>must_change_password</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>既定 FALSE。TRUE の間は初回のパスワード変更を促す（SCR-007 へ誘導）。パスワード変更成功で FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>パスワード変更日時</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>password_changed_at</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>JST。API-023 でパスワードを変更した日時。未変更は NULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
           <t>更新日時</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>TIMESTAMP</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr"/>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>更新時に DB トリガ（set_updated_at / trg_users_updated_at）で自動更新。アプリは設定しない</t>
         </is>
@@ -2099,7 +2226,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
@@ -2266,7 +2392,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
@@ -2549,7 +2674,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
@@ -2836,7 +2960,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
@@ -3147,7 +3270,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>

--- a/docs/02_基本設計/03_データ設計/KF-BD-003_テーブル定義書.xlsx
+++ b/docs/02_基本設計/03_データ設計/KF-BD-003_テーブル定義書.xlsx
@@ -18,7 +18,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="requests" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="approval_steps" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="holidays" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="notifications" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="attendance_breaks" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="notifications" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -529,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="B4:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -541,9 +542,6 @@
     <col width="3" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="1" t="inlineStr">
         <is>
@@ -552,8 +550,6 @@
       </c>
     </row>
     <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -588,7 +584,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="D10" s="10" t="n"/>
@@ -619,8 +615,6 @@
       </c>
       <c r="D12" s="10" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
     <row r="15">
       <c r="D15" s="5" t="inlineStr">
         <is>
@@ -829,7 +823,7 @@
       <c r="E7" s="8" t="inlineStr"/>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>users.id。1段目は作成時に上長を設定。2段目は処理時に実際の承認者（管理者）を設定</t>
+          <t>users.id。1段目は作成時に上長を設定（上長なし・無効な場合は 1 段目を作らず 2 段目のみ）。2段目（管理者）は作成時 NULL で、処理時に実際の承認者を設定</t>
         </is>
       </c>
     </row>
@@ -857,7 +851,7 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>WAITING / APPROVED / RETURNED / REJECTED</t>
+          <t>WAITING / APPROVED / RETURNED / REJECTED（DB に保存する値はこの 4 つ）。API の表示状態 SKIPPED は RequestService#displayStatus による API 層の変換で、DB の値は変わらない</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1061,7 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>一意</t>
+          <t>一意。初期データは V2__seed_holidays.sql（2026〜2027 年の国民の祝日＋年末年始の会社休日 43 件）と V3__seed_holidays_2028.sql（2028 年 21 件）の計 64 件（いずれも ON CONFLICT DO NOTHING）。以降の年は祝日管理（ONL-016）で登録する。</t>
         </is>
       </c>
     </row>
@@ -1154,6 +1148,256 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>テーブル：attendance_breaks（休憩・離席）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>論理名</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>物理名</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>データ型</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>キー</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>休憩・離席ID</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>PK</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>打刻ID</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>attendance_record_id</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>attendance_records.id。索引 idx_attendance_breaks_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>BREAK（休憩）/ AWAY（日中離席）。CHECK ck_attendance_breaks_kind</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>開始日時</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>start_at</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>終了日時</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>end_at</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>NULL＝進行中（終了前）。CHECK ck_attendance_breaks_range（end_at IS NULL OR end_at &gt;= start_at）。進行中は 1 打刻につき 1 件まで（部分一意索引 uq_attendance_breaks_open：attendance_record_id WHERE end_at IS NULL）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>更新日時</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>更新時に DB トリガ（set_updated_at / trg_attendance_breaks_updated_at）で自動更新。アプリは設定しない</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1433,7 +1677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1470,7 +1714,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="23" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -1493,7 +1737,7 @@
       </c>
       <c r="E2" s="8" t="inlineStr"/>
     </row>
-    <row r="3">
+    <row r="3" ht="68" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -1516,7 +1760,7 @@
       </c>
       <c r="E3" s="8" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" ht="68" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>1.2</t>
@@ -1538,6 +1782,52 @@
         </is>
       </c>
       <c r="E4" s="8" t="n"/>
+    </row>
+    <row r="5" ht="173" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>V1__init_schema.sql・JPA Entity との突合結果を反映（列・型・NOT NULL・キーに差異なし）。①holidays に初期データ（V2__seed_holidays.sql：2026〜2027 年の国民の祝日＋年末年始の会社休日 43 件）を追記②requests.current_step の値（0=下書き／1・2=処理待ちの段）、approval_steps.approver_id（上長なし時は 2 段目のみ・2 段目は処理まで NULL）、leave_types.max_days_rule のコード値（LIMITED / UNLIMITED）、users の認証関連列（登録・パスワード設定時の must_change_password=TRUE、パスワード設定によるロック解除）の備考を補足③部署・休暇種別の初期データ（V1）を備考に追記</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr"/>
+    </row>
+    <row r="6" ht="188" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>コード（V3〜V5 マイグレーション・JPA Entity）に合わせて更新。①テーブル attendance_breaks（休憩・日中離席の区間。V4）を追加し、テーブル一覧を 10 テーブルに変更②requests に休憩・離席修正申請用の 3 列（corrected_break_kind / corrected_break_start / corrected_break_end。V5。いずれも NULL 可）を追加し、request_type に BREAK_CORRECTION を追記③holidays の初期データを 64 件に更新（V3__seed_holidays_2028.sql で 2028 年分 21 件を追加）④approval_steps.status の SKIPPED は API 層の表示変換であり DB の値は変わらない旨を追記⑤Flyway は V1〜V5 適用済み、次に追加する版は V6。詳細は KF-DD-003・KF-DD-TBL-05〜08・10 を参照</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1551,7 +1841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1563,7 +1853,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>※データ型は PostgreSQL（Flyway マイグレーション V1__init_schema.sql）に合わせる。物理削除は行わず、状態・有効フラグで管理する。</t>
+          <t>※データ型は PostgreSQL（Flyway マイグレーション V1〜V5。V1__init_schema.sql が基本、V4 が attendance_breaks、V5 が requests の追加列）に合わせる。物理削除は行わず、状態・有効フラグで管理する（例外：祝日・通知）。初期データは V1（部署 5 件・休暇種別 11 件）と V2・V3（祝日。64 件）。V4・V5 は DDL のみ。ユーザーは SQL ではなくアプリ起動時の初期化処理で作成する（詳細は KF-DD-003『初期データ・開発用シード』。開発用データは kintaiflow.dev.seed-enabled=true のときだけ作成）。</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1909,11 @@
           <t>departments</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>初期データ 5 件（V1）</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
@@ -1651,7 +1945,11 @@
           <t>leave_types</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>初期データ 11 件（法定休暇。V1）</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
@@ -1715,7 +2013,11 @@
           <t>holidays</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr"/>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>初期データ 64 件（V2：2026〜2027 年 43 件、V3：2028 年 21 件）。以降の年は祝日管理（ONL-016）で登録</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
@@ -1732,6 +2034,26 @@
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>休憩・離席</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>attendance_breaks</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>打刻記録に紐づく休憩・日中離席の区間（V4）</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1763,7 +2085,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
@@ -2064,7 +2385,7 @@
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>既定 0。パスワード不一致のたびに +1。5 回でロックし 0 に戻す。ログイン成功でも 0 に戻す</t>
+          <t>既定 0。パスワード不一致のたびに +1（ログイン・パスワード変更）。5 回でロックし 0 に戻す。ログイン成功・管理者のパスワード設定でも 0 に戻す</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2409,7 @@
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>JST。NULL＝ロックなし。現在時刻がこの日時より前ならロック中（E-017）。ロック開始から 30 分後を設定</t>
+          <t>JST。NULL＝ロックなし。現在時刻がこの日時より前ならロック中（E-017）。ロック開始から 30 分後を設定。管理者のパスワード設定で NULL に戻る（手動解除を兼ねる）</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2437,7 @@
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>既定 FALSE。TRUE の間は初回のパスワード変更を促す（SCR-007 へ誘導）。パスワード変更成功で FALSE</t>
+          <t>既定 FALSE。ユーザー登録・管理者のパスワード設定・初期管理者作成時に TRUE。TRUE の間は初回のパスワード変更を促し（SCR-007 へ誘導）、サーバーもパスワード変更 API 以外を拒否する（E-019）。パスワード変更成功で FALSE</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2629,11 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>初期データ 5 件（V1）：管理部／システム開発事業部／ソリューション事業部／SAP事業部／クラウド基盤サービス部</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -2570,7 +2895,11 @@
       </c>
       <c r="D9" s="8" t="inlineStr"/>
       <c r="E9" s="8" t="inlineStr"/>
-      <c r="F9" s="8" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>休憩・日中離席の控除後の分。区間は attendance_breaks に保存（V4。AttendanceCalculator が控除）</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -2826,7 +3155,7 @@
       <c r="E8" s="8" t="inlineStr"/>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>上限付き / 無制限</t>
+          <t>LIMITED（上限付き）/ UNLIMITED（無制限）</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3386,7 +3715,7 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>LEAVE / CLOCK_CORRECTION</t>
+          <t>LEAVE / CLOCK_CORRECTION / BREAK_CORRECTION（V5 で追加。CHECK ck_req_type）</t>
         </is>
       </c>
     </row>
@@ -3565,89 +3894,89 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>理由</t>
+          <t>修正後休憩・離席の種別</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>corrected_break_kind</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>VARCHAR(200)</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr"/>
-      <c r="E14" s="8" t="inlineStr"/>
-      <c r="F14" s="8" t="inlineStr"/>
+          <t>VARCHAR(10)</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>休憩・離席修正申請（BREAK_CORRECTION）のみ。BREAK / AWAY（CHECK ck_req_break_kind）。V5 で追加</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>状態</t>
+          <t>修正後休憩・離席の開始</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>corrected_break_start</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr"/>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>DRAFT / PENDING / RETURNED / REJECTED / APPROVED / WITHDRAWN</t>
+          <t>休憩・離席修正申請のみ。V5 で追加</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>現在の承認段</t>
+          <t>修正後休憩・離席の終了</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>current_step</t>
+          <t>corrected_break_end</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr"/>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr"/>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>休憩・離席修正申請のみ。V5 で追加</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>提出日時</t>
+          <t>理由</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>submitted_at</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR(200)</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr"/>
@@ -3657,17 +3986,17 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>状態</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>status</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr"/>
@@ -3676,22 +4005,26 @@
           <t>○</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr"/>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>DRAFT / PENDING / RETURNED / REJECTED / APPROVED / WITHDRAWN</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>現在の承認段</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>current_step</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr"/>
@@ -3701,6 +4034,78 @@
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>0：下書き（承認ルート未作成）／1・2：処理待ちの段（上長なしは 2）。承認・差戻し・却下・取下げ後は最後の段のまま</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>提出日時</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>submitted_at</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="8" t="inlineStr"/>
+      <c r="F20" s="8" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>更新日時</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr"/>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>更新時に DB トリガ（set_updated_at / trg_requests_updated_at）で自動更新。アプリは設定しない</t>
         </is>
